--- a/artfynd/A 16859-2026 artfynd.xlsx
+++ b/artfynd/A 16859-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132537326</v>
+        <v>132536832</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585737</v>
+        <v>585698</v>
       </c>
       <c r="R2" t="n">
-        <v>6320754</v>
+        <v>6320677</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132536832</v>
+        <v>132537180</v>
       </c>
       <c r="B3" t="n">
-        <v>91918</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585698</v>
+        <v>585737</v>
       </c>
       <c r="R3" t="n">
-        <v>6320677</v>
+        <v>6320754</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,35 +869,40 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132537180</v>
+        <v>132537326</v>
       </c>
       <c r="B4" t="n">
-        <v>91918</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nybygget, Nybygget, Sm</t>
